--- a/assets/data/SpaceWar_Data.xlsx
+++ b/assets/data/SpaceWar_Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mians\Documents\space-war\assets\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2B2FC3BA-A8AB-4E2E-B9AA-B1574009159F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C834521-CC1F-4B32-B6DE-78BD69D8586F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{4991EE2C-363E-439C-B1C2-C17965695B32}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
   <si>
     <t>step</t>
   </si>
@@ -51,6 +51,60 @@
   </si>
   <si>
     <t>Snapped</t>
+  </si>
+  <si>
+    <t>Object</t>
+  </si>
+  <si>
+    <t>Layer</t>
+  </si>
+  <si>
+    <t>Mask</t>
+  </si>
+  <si>
+    <t>Comment</t>
+  </si>
+  <si>
+    <t>Player</t>
+  </si>
+  <si>
+    <t>Player Bullet</t>
+  </si>
+  <si>
+    <t>Enemy</t>
+  </si>
+  <si>
+    <t>Enemy Bullet</t>
+  </si>
+  <si>
+    <t>玩家第一层，被敌人检测</t>
+  </si>
+  <si>
+    <t>玩家子弹打敌人</t>
+  </si>
+  <si>
+    <t>敌人被玩家子弹打中</t>
+  </si>
+  <si>
+    <t>敌人的子弹打玩家</t>
+  </si>
+  <si>
+    <t>Ground</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>Enemy Detector</t>
+  </si>
+  <si>
+    <t>只检测玩家</t>
+  </si>
+  <si>
+    <t>3,2</t>
+  </si>
+  <si>
+    <t>3,5,6</t>
   </si>
 </sst>
 </file>
@@ -80,7 +134,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -88,13 +142,31 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -436,6 +508,9 @@
     <col min="4" max="4" width="18.42578125" customWidth="1"/>
     <col min="5" max="5" width="17.85546875" customWidth="1"/>
     <col min="6" max="6" width="21.7109375" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.42578125" customWidth="1"/>
+    <col min="15" max="15" width="26.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:20" x14ac:dyDescent="0.25">
@@ -807,6 +882,18 @@
         <f t="shared" si="1"/>
         <v>23</v>
       </c>
+      <c r="L24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M24" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="N24" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="O24" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="25" spans="4:20" x14ac:dyDescent="0.25">
       <c r="D25">
@@ -820,6 +907,18 @@
         <f t="shared" si="1"/>
         <v>45</v>
       </c>
+      <c r="L25" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="M25" s="2">
+        <v>1</v>
+      </c>
+      <c r="N25" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="O25" s="2" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="26" spans="4:20" x14ac:dyDescent="0.25">
       <c r="D26">
@@ -833,6 +932,18 @@
         <f t="shared" si="1"/>
         <v>45</v>
       </c>
+      <c r="L26" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="M26" s="2">
+        <v>2</v>
+      </c>
+      <c r="N26" s="2">
+        <v>4</v>
+      </c>
+      <c r="O26" s="2" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="27" spans="4:20" x14ac:dyDescent="0.25">
       <c r="D27">
@@ -846,6 +957,18 @@
         <f t="shared" si="1"/>
         <v>45</v>
       </c>
+      <c r="L27" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M27" s="2">
+        <v>4</v>
+      </c>
+      <c r="N27" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="O27" s="2" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="28" spans="4:20" x14ac:dyDescent="0.25">
       <c r="D28">
@@ -859,6 +982,18 @@
         <f t="shared" si="1"/>
         <v>45</v>
       </c>
+      <c r="L28" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="M28" s="2">
+        <v>8</v>
+      </c>
+      <c r="N28" s="2">
+        <v>1</v>
+      </c>
+      <c r="O28" s="2" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="29" spans="4:20" x14ac:dyDescent="0.25">
       <c r="D29">
@@ -872,6 +1007,16 @@
         <f t="shared" si="1"/>
         <v>45</v>
       </c>
+      <c r="L29" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="M29" s="4">
+        <v>3</v>
+      </c>
+      <c r="N29" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="O29" s="2"/>
     </row>
     <row r="30" spans="4:20" x14ac:dyDescent="0.25">
       <c r="D30">
@@ -884,6 +1029,18 @@
       <c r="F30">
         <f t="shared" si="1"/>
         <v>45</v>
+      </c>
+      <c r="L30" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="M30" s="4">
+        <v>6</v>
+      </c>
+      <c r="N30" s="2">
+        <v>1</v>
+      </c>
+      <c r="O30" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="31" spans="4:20" x14ac:dyDescent="0.25">

--- a/assets/data/SpaceWar_Data.xlsx
+++ b/assets/data/SpaceWar_Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mians\Documents\space-war\assets\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C834521-CC1F-4B32-B6DE-78BD69D8586F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A6A58B9-F343-4901-A12C-22FC54C49BA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{4991EE2C-363E-439C-B1C2-C17965695B32}"/>
+    <workbookView xWindow="38280" yWindow="5415" windowWidth="29040" windowHeight="15720" xr2:uid="{4991EE2C-363E-439C-B1C2-C17965695B32}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
   <si>
     <t>step</t>
   </si>
@@ -105,6 +105,12 @@
   </si>
   <si>
     <t>3,5,6</t>
+  </si>
+  <si>
+    <t>Coin</t>
+  </si>
+  <si>
+    <t>1,3</t>
   </si>
 </sst>
 </file>
@@ -1007,10 +1013,10 @@
         <f t="shared" si="1"/>
         <v>45</v>
       </c>
-      <c r="L29" s="4" t="s">
+      <c r="L29" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="M29" s="4">
+      <c r="M29" s="2">
         <v>3</v>
       </c>
       <c r="N29" s="2" t="s">
@@ -1030,10 +1036,10 @@
         <f t="shared" si="1"/>
         <v>45</v>
       </c>
-      <c r="L30" s="4" t="s">
+      <c r="L30" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="M30" s="4">
+      <c r="M30" s="2">
         <v>6</v>
       </c>
       <c r="N30" s="2">
@@ -1055,6 +1061,16 @@
         <f t="shared" si="1"/>
         <v>45</v>
       </c>
+      <c r="L31" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="M31" s="4">
+        <v>9</v>
+      </c>
+      <c r="N31" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="O31" s="2"/>
     </row>
     <row r="32" spans="4:20" x14ac:dyDescent="0.25">
       <c r="D32">
